--- a/WCAG_22_AA_Extension_Issues_Validation.xlsx
+++ b/WCAG_22_AA_Extension_Issues_Validation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\Accessibility\Axe Core Coverage\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F777FF2-5B8A-4BDB-93EB-DAFDBEF23775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26CE4A6-3B9B-4D61-925A-0F59C7A74145}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{7EB49925-5ECB-460B-91D1-37898B1C3425}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="153">
   <si>
     <t>Success Criterion</t>
   </si>
@@ -7670,6 +7670,9 @@
   </si>
   <si>
     <t>Result Removed from violations as part of algo improvement</t>
+  </si>
+  <si>
+    <t>Result Removed from violations as part of algo improvement, 1.0.3</t>
   </si>
 </sst>
 </file>
@@ -9882,6 +9885,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6276E77-4CB8-47D0-A25E-A5A9A9F2FE8A}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:Z88"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
@@ -9927,7 +9931,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -9959,7 +9963,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -9989,7 +9993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -10019,7 +10023,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -10049,7 +10053,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -10079,7 +10083,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -10109,7 +10113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -10139,7 +10143,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -10166,7 +10170,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -10195,7 +10199,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -10222,7 +10226,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -10249,7 +10253,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="13" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -10276,7 +10280,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
         <v>13</v>
       </c>
@@ -10303,7 +10307,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -10330,7 +10334,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:26" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
         <v>15</v>
       </c>
@@ -10357,7 +10361,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="17" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>16</v>
       </c>
@@ -10384,7 +10388,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>17</v>
       </c>
@@ -10411,7 +10415,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="19" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -10438,7 +10442,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="20" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>19</v>
       </c>
@@ -10465,7 +10469,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="21" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>20</v>
       </c>
@@ -10492,7 +10496,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="22" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>21</v>
       </c>
@@ -10519,7 +10523,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="23" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>22</v>
       </c>
@@ -10546,7 +10550,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="24" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>23</v>
       </c>
@@ -10892,7 +10896,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="36" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>35</v>
       </c>
@@ -10919,7 +10923,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>36</v>
       </c>
@@ -10946,7 +10950,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>37</v>
       </c>
@@ -10973,7 +10977,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>38</v>
       </c>
@@ -11000,7 +11004,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="40" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>39</v>
       </c>
@@ -11027,7 +11031,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="41" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>40</v>
       </c>
@@ -11054,7 +11058,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>41</v>
       </c>
@@ -11081,7 +11085,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="43" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>42</v>
       </c>
@@ -11108,7 +11112,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="44" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>43</v>
       </c>
@@ -11135,7 +11139,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="45" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>44</v>
       </c>
@@ -11162,7 +11166,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="46" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>45</v>
       </c>
@@ -11189,7 +11193,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>46</v>
       </c>
@@ -11216,7 +11220,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="48" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>47</v>
       </c>
@@ -11245,7 +11249,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="49" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>48</v>
       </c>
@@ -11274,7 +11278,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="50" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>49</v>
       </c>
@@ -11301,7 +11305,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="51" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>50</v>
       </c>
@@ -11328,7 +11332,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="52" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>51</v>
       </c>
@@ -11355,7 +11359,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="53" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>52</v>
       </c>
@@ -11382,7 +11386,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="54" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>53</v>
       </c>
@@ -11409,7 +11413,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="55" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>54</v>
       </c>
@@ -11436,7 +11440,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="56" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>55</v>
       </c>
@@ -11463,7 +11467,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="57" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>56</v>
       </c>
@@ -11490,7 +11494,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="58" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>57</v>
       </c>
@@ -11519,7 +11523,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="59" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>58</v>
       </c>
@@ -11546,7 +11550,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="60" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>59</v>
       </c>
@@ -11575,7 +11579,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>60</v>
       </c>
@@ -11602,7 +11606,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="62" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>61</v>
       </c>
@@ -11629,7 +11633,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="63" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>62</v>
       </c>
@@ -11656,7 +11660,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="64" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>63</v>
       </c>
@@ -11683,7 +11687,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>64</v>
       </c>
@@ -11712,7 +11716,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>65</v>
       </c>
@@ -11741,7 +11745,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>66</v>
       </c>
@@ -11768,7 +11772,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>67</v>
       </c>
@@ -11797,7 +11801,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="69" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>68</v>
       </c>
@@ -11824,7 +11828,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="70" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>69</v>
       </c>
@@ -11853,7 +11857,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>70</v>
       </c>
@@ -11880,7 +11884,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="72" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>71</v>
       </c>
@@ -11907,7 +11911,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="73" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>72</v>
       </c>
@@ -11934,7 +11938,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>73</v>
       </c>
@@ -11961,7 +11965,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>74</v>
       </c>
@@ -11988,7 +11992,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="76" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>75</v>
       </c>
@@ -12015,7 +12019,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="77" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>76</v>
       </c>
@@ -12042,7 +12046,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="78" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>77</v>
       </c>
@@ -12069,7 +12073,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>78</v>
       </c>
@@ -12098,7 +12102,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="80" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>79</v>
       </c>
@@ -12212,7 +12216,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="84" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>83</v>
       </c>
@@ -12239,7 +12243,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="85" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>84</v>
       </c>
@@ -12266,7 +12270,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="86" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>85</v>
       </c>
@@ -12295,7 +12299,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="87" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>86</v>
       </c>
@@ -12317,12 +12321,14 @@
       <c r="G87" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H87" s="3"/>
+      <c r="H87" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="I87" s="7" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="88" spans="1:9" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" ht="39.950000000000003" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>87</v>
       </c>
@@ -12344,13 +12350,27 @@
       <c r="G88" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="H88" s="3"/>
+      <c r="H88" s="3" t="s">
+        <v>152</v>
+      </c>
       <c r="I88" s="7" t="s">
         <v>150</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I88" xr:uid="{F6276E77-4CB8-47D0-A25E-A5A9A9F2FE8A}"/>
+  <autoFilter ref="A1:I88" xr:uid="{F6276E77-4CB8-47D0-A25E-A5A9A9F2FE8A}">
+    <filterColumn colId="5">
+      <filters>
+        <filter val="No"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="7">
+      <filters>
+        <filter val="Determine how to exclude elements when a modal popup is active"/>
+        <filter val="Tooltip, intended by html, is not appearing after hovering on the page"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G24 G36:G88" xr:uid="{1C7F3733-AA40-4553-8F33-17AEC86B86D1}">
       <formula1>Reasons</formula1>
